--- a/hardware/BOM.xlsx
+++ b/hardware/BOM.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11008"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11013"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5F62B52-612B-7F4C-B855-25D66BA1DAC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C181C1D0-A242-4C49-9805-C49D540D6597}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12120" yWindow="6140" windowWidth="32680" windowHeight="17700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12120" yWindow="5700" windowWidth="32680" windowHeight="17700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_AVR Touch Pad_AVR Touch Pad" sheetId="1" r:id="rId1"/>
@@ -80,7 +80,7 @@
     <t>nRF24</t>
   </si>
   <si>
-    <t>ATMega 8/48/168/328</t>
+    <t>ATMega 168/328</t>
   </si>
 </sst>
 </file>
@@ -480,9 +480,9 @@
   <cols>
     <col min="1" max="1" width="3.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
